--- a/data/trans_dic/P2A_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P2A_R-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con alguna limitación</t>
+          <t>Hogares con personas con alguna limitación (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>35,84; 56,89</t>
+          <t>36,81; 58,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>36,0; 57,94</t>
+          <t>35,55; 57,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34,39; 59,33</t>
+          <t>34,07; 58,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43,12; 75,68</t>
+          <t>42,66; 75,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>50,95; 72,35</t>
+          <t>51,73; 72,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,72; 52,85</t>
+          <t>33,31; 52,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,72; 49,01</t>
+          <t>26,63; 47,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>56,36; 77,58</t>
+          <t>56,88; 78,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>46,15; 62,24</t>
+          <t>45,13; 61,02</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37,27; 52,51</t>
+          <t>36,96; 52,37</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33,25; 50,34</t>
+          <t>32,63; 49,46</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>53,92; 74,33</t>
+          <t>53,81; 73,87</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>28,3; 36,91</t>
+          <t>27,96; 36,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>29,91; 38,46</t>
+          <t>29,73; 38,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27,79; 35,89</t>
+          <t>28,48; 36,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>76,32; 84,1</t>
+          <t>76,33; 84,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,42; 39,37</t>
+          <t>31,33; 39,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,72; 40,03</t>
+          <t>31,59; 39,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,76; 37,41</t>
+          <t>29,83; 37,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>69,37; 79,84</t>
+          <t>69,09; 79,74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31,06; 36,96</t>
+          <t>31,32; 37,38</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31,86; 37,75</t>
+          <t>31,88; 37,79</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30,31; 35,97</t>
+          <t>30,13; 35,98</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>74,4; 80,63</t>
+          <t>74,37; 80,79</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22,88; 35,73</t>
+          <t>23,21; 35,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27,16; 41,73</t>
+          <t>27,3; 42,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28,16; 41,41</t>
+          <t>28,53; 42,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>71,04; 82,58</t>
+          <t>71,04; 82,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26,26; 39,55</t>
+          <t>26,41; 40,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,34; 37,67</t>
+          <t>24,54; 37,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,85; 37,63</t>
+          <t>25,07; 37,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>72,0; 83,1</t>
+          <t>71,17; 83,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26,48; 35,39</t>
+          <t>26,1; 35,58</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27,49; 37,06</t>
+          <t>27,44; 37,53</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28,37; 37,76</t>
+          <t>28,4; 38,27</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>73,12; 81,42</t>
+          <t>73,06; 81,27</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29,64; 36,33</t>
+          <t>29,7; 36,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>31,76; 39,16</t>
+          <t>32,1; 39,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30,69; 37,3</t>
+          <t>31,04; 37,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74,63; 81,58</t>
+          <t>74,28; 81,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>33,89; 40,4</t>
+          <t>33,88; 40,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,81; 38,71</t>
+          <t>32,03; 38,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,28; 36,87</t>
+          <t>30,35; 36,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>71,22; 78,63</t>
+          <t>71,37; 79,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>32,83; 37,65</t>
+          <t>32,76; 37,45</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32,69; 37,54</t>
+          <t>32,85; 37,92</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31,33; 36,24</t>
+          <t>31,23; 35,92</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>73,64; 79,03</t>
+          <t>74,04; 79,25</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hogares con personas con alguna limitación (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>25830</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>25793</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>18822</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>34366</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>31941</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>26440</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>19094</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>42453</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>57771</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>52232</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>37916</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>76819</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>20786; 32824</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>19725; 31852</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>13844; 23707</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>23327; 41359</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>26577; 37152</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>20685; 32682</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>13645; 24302</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>35266; 48676</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>48669; 65798</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>43451; 61570</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>29979; 45444</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>62782; 86193</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>505</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>521</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>1026</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>100250</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>103602</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>112739</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>367721</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>125043</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>121147</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>127957</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>391414</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>225294</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>224749</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>240696</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>759135</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>86776; 112025</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>90584; 117514</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>99325; 126836</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>351501; 387146</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>110784; 139775</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>107328; 135835</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>113306; 143284</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>356940; 411946</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>207958; 248186</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>205425; 243543</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>219490; 262172</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>726689; 789381</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>367</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>39556</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>39675</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>47583</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>115242</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>40226</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>41732</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>43292</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>142583</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>79782</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>81407</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>90875</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>257825</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>31700; 48735</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>31896; 49101</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>38815; 57477</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>106239; 123314</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>32626; 49941</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>33593; 51853</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>35075; 52814</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>130484; 152356</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>67899; 92562</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>69617; 95222</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>78365; 105619</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>243224; 270553</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>730</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>765</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>543</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>543</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1495</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>165636</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>169071</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>179144</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>517328</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>197211</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>189318</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>190343</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>576450</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>362846</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>358388</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>369487</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>1093778</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>149513; 182265</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>153090; 187837</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>163082; 198848</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>493743; 540208</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>179082; 213526</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>172586; 208284</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>173316; 207870</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>543841; 602518</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>338020; 386435</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>333641; 385221</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>342393; 393868</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>1056268; 1130731</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/P2A_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P2A_R-Estudios-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>36,81; 58,13</t>
+          <t>35,0; 56,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>35,55; 57,41</t>
+          <t>35,99; 58,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34,07; 58,33</t>
+          <t>33,69; 59,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42,66; 75,64</t>
+          <t>42,22; 76,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>51,73; 72,32</t>
+          <t>50,73; 73,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,31; 52,64</t>
+          <t>32,72; 53,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,63; 47,43</t>
+          <t>26,76; 48,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>56,88; 78,51</t>
+          <t>56,54; 78,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>45,13; 61,02</t>
+          <t>45,8; 60,88</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36,96; 52,37</t>
+          <t>37,15; 52,36</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32,63; 49,46</t>
+          <t>32,81; 50,0</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>53,81; 73,87</t>
+          <t>53,57; 73,41</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>27,96; 36,1</t>
+          <t>28,49; 36,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>29,73; 38,57</t>
+          <t>29,46; 38,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28,48; 36,37</t>
+          <t>28,02; 36,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>76,33; 84,07</t>
+          <t>76,49; 84,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,33; 39,53</t>
+          <t>31,38; 39,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,59; 39,98</t>
+          <t>31,03; 39,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,83; 37,72</t>
+          <t>29,51; 37,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>69,09; 79,74</t>
+          <t>70,0; 79,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31,32; 37,38</t>
+          <t>31,18; 36,97</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31,88; 37,79</t>
+          <t>31,68; 37,93</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30,13; 35,98</t>
+          <t>30,45; 36,18</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>74,37; 80,79</t>
+          <t>73,86; 80,68</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23,21; 35,68</t>
+          <t>23,09; 36,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27,3; 42,03</t>
+          <t>26,98; 42,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28,53; 42,25</t>
+          <t>28,21; 42,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>71,04; 82,46</t>
+          <t>71,26; 82,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26,41; 40,42</t>
+          <t>26,12; 39,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,54; 37,88</t>
+          <t>23,86; 37,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,07; 37,74</t>
+          <t>24,63; 37,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>71,17; 83,1</t>
+          <t>71,76; 83,24</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26,1; 35,58</t>
+          <t>25,97; 35,36</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27,44; 37,53</t>
+          <t>27,01; 37,02</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28,4; 38,27</t>
+          <t>28,8; 37,99</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>73,06; 81,27</t>
+          <t>73,23; 81,12</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29,7; 36,21</t>
+          <t>29,43; 36,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>32,1; 39,38</t>
+          <t>32,1; 39,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31,04; 37,85</t>
+          <t>30,92; 37,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74,28; 81,27</t>
+          <t>74,29; 81,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>33,88; 40,4</t>
+          <t>33,95; 40,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,03; 38,66</t>
+          <t>32,02; 38,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,35; 36,4</t>
+          <t>29,68; 36,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>71,37; 79,07</t>
+          <t>71,53; 78,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>32,76; 37,45</t>
+          <t>32,73; 37,63</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32,85; 37,92</t>
+          <t>32,81; 37,88</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31,23; 35,92</t>
+          <t>31,59; 36,2</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>74,04; 79,25</t>
+          <t>73,72; 78,89</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>20786; 32824</t>
+          <t>19762; 31930</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19725; 31852</t>
+          <t>19969; 32284</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13844; 23707</t>
+          <t>13691; 24106</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23327; 41359</t>
+          <t>23088; 42029</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>26577; 37152</t>
+          <t>26058; 37609</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20685; 32682</t>
+          <t>20313; 33168</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13645; 24302</t>
+          <t>13712; 24927</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>35266; 48676</t>
+          <t>35059; 48502</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>48669; 65798</t>
+          <t>49385; 65648</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>43451; 61570</t>
+          <t>43684; 61562</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29979; 45444</t>
+          <t>30144; 45938</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>62782; 86193</t>
+          <t>62502; 85659</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>86776; 112025</t>
+          <t>88411; 114605</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>90584; 117514</t>
+          <t>89751; 116689</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>99325; 126836</t>
+          <t>97696; 126556</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>351501; 387146</t>
+          <t>352245; 389147</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>110784; 139775</t>
+          <t>110955; 140434</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>107328; 135835</t>
+          <t>105452; 135058</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>113306; 143284</t>
+          <t>112110; 143692</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>356940; 411946</t>
+          <t>361616; 412997</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>207958; 248186</t>
+          <t>207026; 245463</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>205425; 243543</t>
+          <t>204182; 244450</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>219490; 262172</t>
+          <t>221835; 263595</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>726689; 789381</t>
+          <t>721688; 788355</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>31700; 48735</t>
+          <t>31542; 49519</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>31896; 49101</t>
+          <t>31515; 49213</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38815; 57477</t>
+          <t>38377; 57561</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>106239; 123314</t>
+          <t>106569; 123238</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>32626; 49941</t>
+          <t>32265; 48734</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>33593; 51853</t>
+          <t>32671; 51280</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35075; 52814</t>
+          <t>34471; 52943</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>130484; 152356</t>
+          <t>131567; 152619</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>67899; 92562</t>
+          <t>67545; 91989</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>69617; 95222</t>
+          <t>68536; 93937</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>78365; 105619</t>
+          <t>79463; 104830</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>243224; 270553</t>
+          <t>243794; 270055</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>149513; 182265</t>
+          <t>148119; 182107</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>153090; 187837</t>
+          <t>153097; 186219</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>163082; 198848</t>
+          <t>162427; 199215</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>493743; 540208</t>
+          <t>493834; 542286</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>179082; 213526</t>
+          <t>179464; 214454</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>172586; 208284</t>
+          <t>172497; 208367</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>173316; 207870</t>
+          <t>169476; 207926</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>543841; 602518</t>
+          <t>545068; 601628</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>338020; 386435</t>
+          <t>337770; 388260</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>333641; 385221</t>
+          <t>333254; 384731</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>342393; 393868</t>
+          <t>346326; 396908</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1056268; 1130731</t>
+          <t>1051754; 1125553</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P2A_R-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>62,18%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>42,58%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>37,27%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>68,82%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>45,75%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>46,49%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>46,31%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>62,85%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>62,18%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>42,58%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>37,27%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>68,29%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>35,0; 56,55</t>
+          <t>50,95; 72,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>35,99; 58,19</t>
+          <t>31,72; 52,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33,69; 59,31</t>
+          <t>26,72; 49,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42,22; 76,87</t>
+          <t>56,46; 78,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>50,73; 73,21</t>
+          <t>35,84; 56,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,72; 53,42</t>
+          <t>36,0; 57,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,76; 48,65</t>
+          <t>34,39; 59,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>56,54; 78,22</t>
+          <t>55,98; 78,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>45,8; 60,88</t>
+          <t>46,15; 62,24</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37,15; 52,36</t>
+          <t>37,27; 52,51</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32,81; 50,0</t>
+          <t>33,25; 50,34</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>53,57; 73,41</t>
+          <t>59,21; 75,22</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>35,36%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>35,65%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>33,68%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>77,41%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>32,31%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>34,01%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>32,33%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>79,85%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>35,36%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>35,65%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>33,68%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>77,93%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>28,49; 36,93</t>
+          <t>31,42; 39,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>29,46; 38,3</t>
+          <t>31,72; 40,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28,02; 36,29</t>
+          <t>29,76; 37,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>76,49; 84,5</t>
+          <t>71,75; 81,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,38; 39,71</t>
+          <t>28,3; 36,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,03; 39,75</t>
+          <t>29,91; 38,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,51; 37,83</t>
+          <t>27,79; 35,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>70,0; 79,94</t>
+          <t>75,12; 81,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31,18; 36,97</t>
+          <t>31,06; 36,96</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31,68; 37,93</t>
+          <t>31,86; 37,75</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30,45; 36,18</t>
+          <t>30,31; 35,97</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>73,86; 80,68</t>
+          <t>75,01; 80,38</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>32,56%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>30,48%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>30,94%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>78,25%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>28,96%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>33,96%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>34,98%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>77,06%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>32,56%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>30,48%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>30,94%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,93%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23,09; 36,26</t>
+          <t>26,26; 39,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26,98; 42,12</t>
+          <t>24,34; 37,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28,21; 42,32</t>
+          <t>24,85; 37,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>71,26; 82,41</t>
+          <t>72,21; 83,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26,12; 39,45</t>
+          <t>22,88; 35,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,86; 37,46</t>
+          <t>27,16; 41,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,63; 37,84</t>
+          <t>28,16; 41,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>71,76; 83,24</t>
+          <t>71,35; 82,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25,97; 35,36</t>
+          <t>26,48; 35,39</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27,01; 37,02</t>
+          <t>27,49; 37,06</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28,8; 37,99</t>
+          <t>28,37; 37,76</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>73,23; 81,12</t>
+          <t>73,63; 81,57</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>37,31%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>35,14%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>33,33%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>76,91%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>32,91%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>35,45%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>34,1%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>77,82%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>37,31%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>35,14%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>33,33%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>77,18%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29,43; 36,18</t>
+          <t>33,89; 40,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>32,1; 39,04</t>
+          <t>31,81; 38,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30,92; 37,92</t>
+          <t>30,28; 36,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74,29; 81,58</t>
+          <t>73,12; 79,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>33,95; 40,57</t>
+          <t>29,64; 36,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,02; 38,67</t>
+          <t>31,76; 39,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,68; 36,41</t>
+          <t>30,69; 37,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>71,53; 78,96</t>
+          <t>74,67; 80,27</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>32,73; 37,63</t>
+          <t>32,83; 37,65</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32,81; 37,88</t>
+          <t>32,69; 37,54</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31,59; 36,2</t>
+          <t>31,33; 36,24</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>73,72; 78,89</t>
+          <t>74,76; 79,22</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,42 +1368,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>46</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>31941</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>26440</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>19094</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>39041</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>25830</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>25793</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>18822</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>34366</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>31941</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>26440</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>19094</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>42453</t>
+          <t>31633</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>76819</t>
+          <t>70674</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>19762; 31930</t>
+          <t>26175; 37165</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19969; 32284</t>
+          <t>19695; 32813</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13691; 24106</t>
+          <t>13693; 25112</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23088; 42029</t>
+          <t>32029; 44451</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>26058; 37609</t>
+          <t>20238; 32122</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20313; 33168</t>
+          <t>19973; 32149</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13712; 24927</t>
+          <t>13977; 24113</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>35059; 48502</t>
+          <t>26177; 36779</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>49385; 65648</t>
+          <t>49762; 67119</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>43684; 61562</t>
+          <t>43817; 61738</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30144; 45938</t>
+          <t>30552; 46248</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>62502; 85659</t>
+          <t>61273; 77843</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>521</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>151</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>147</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>168</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>505</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>521</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>125043</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>121147</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>127957</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>368216</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>100250</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>103602</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>112739</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>367721</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>125043</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>121147</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>127957</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>391414</t>
+          <t>339453</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>759135</t>
+          <t>707669</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>88411; 114605</t>
+          <t>111109; 139210</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>89751; 116689</t>
+          <t>107766; 136025</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>97696; 126556</t>
+          <t>113034; 142100</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>352245; 389147</t>
+          <t>341303; 385644</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>110955; 140434</t>
+          <t>87811; 114550</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>105452; 135058</t>
+          <t>91108; 117163</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>112110; 143692</t>
+          <t>96898; 125154</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>361616; 412997</t>
+          <t>324846; 354373</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>207026; 245463</t>
+          <t>206228; 245390</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>204182; 244450</t>
+          <t>205297; 243303</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>221835; 263595</t>
+          <t>220860; 262103</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>721688; 788355</t>
+          <t>681220; 729977</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>179</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>40226</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>41732</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>43292</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>131782</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>39556</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>39675</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>47583</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>115242</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>40226</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>41732</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>43292</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>142583</t>
+          <t>116327</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>257825</t>
+          <t>248110</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>31542; 49519</t>
+          <t>32445; 48857</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>31515; 49213</t>
+          <t>33326; 51571</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38377; 57561</t>
+          <t>34775; 52658</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>106569; 123238</t>
+          <t>121611; 140815</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>32265; 48734</t>
+          <t>31253; 48794</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32671; 51280</t>
+          <t>31727; 48746</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>34471; 52943</t>
+          <t>38305; 56331</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>131567; 152619</t>
+          <t>107009; 124158</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>67545; 91989</t>
+          <t>68885; 92052</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>68536; 93937</t>
+          <t>69750; 94030</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>79463; 104830</t>
+          <t>78296; 104206</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>243794; 270055</t>
+          <t>234422; 259699</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>765</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>241</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>266</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>730</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>297</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>765</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>197211</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>189318</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>190343</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>539040</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>165636</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>169071</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>179144</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>517328</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>197211</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>189318</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>190343</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>576450</t>
+          <t>487413</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1093778</t>
+          <t>1026453</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>148119; 182107</t>
+          <t>179147; 213532</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>153097; 186219</t>
+          <t>171369; 208553</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>162427; 199215</t>
+          <t>172936; 210538</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>493834; 542286</t>
+          <t>512446; 559254</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>179464; 214454</t>
+          <t>149198; 182885</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>172497; 208367</t>
+          <t>151473; 186786</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>169476; 207926</t>
+          <t>161254; 195993</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>545068; 601628</t>
+          <t>469815; 505058</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>337770; 388260</t>
+          <t>338740; 388537</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>333254; 384731</t>
+          <t>332062; 381335</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>346326; 396908</t>
+          <t>343486; 397367</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1051754; 1125553</t>
+          <t>994310; 1053621</t>
         </is>
       </c>
     </row>
